--- a/Result/checksunmy.xlsx
+++ b/Result/checksunmy.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -1897,11 +1897,15 @@
           <t>144.55</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>146.02</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>161.98</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>146.02</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>161.98</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2654,7 +2658,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2669,7 +2673,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -2883,11 +2887,15 @@
           <t>145.0</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>146.57</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>163</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>146.57</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3640,7 +3648,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -3655,7 +3663,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -3869,11 +3877,15 @@
           <t>145.2</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>147.28</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>163.98</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>147.28</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>163.98</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4626,7 +4638,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -4641,7 +4653,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -4855,11 +4867,15 @@
           <t>145.35</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>147.9</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>164.61</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>147.9</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>164.61</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5612,7 +5628,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -5627,7 +5643,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -5841,11 +5857,15 @@
           <t>145.7</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>148.8</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>165.39</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>148.8</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>165.39</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6598,7 +6618,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -6613,7 +6633,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -6827,11 +6847,15 @@
           <t>145.8</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>149.45</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>166.15</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>149.45</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>166.15</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7584,7 +7608,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -7599,7 +7623,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -7813,11 +7837,15 @@
           <t>146.35</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>150.25</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>167.04</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>150.25</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>167.04</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8570,7 +8598,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -8585,7 +8613,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
@@ -8799,11 +8827,15 @@
           <t>146.55</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>150.93</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>168.01</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>150.93</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>168.01</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9556,7 +9588,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -9571,7 +9603,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -9785,11 +9817,15 @@
           <t>147.15</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>151.62</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>169.04</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>151.62</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>169.04</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10522,17 +10558,17 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -10542,7 +10578,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -10552,27 +10588,27 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10771,11 +10807,15 @@
           <t>2410.0</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>2284.25</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>1968.9</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>2284.25</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>1968.9</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -11503,24 +11543,24 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
       <c r="AU12" t="inlineStr">
         <is>
           <t>False</t>
@@ -11528,7 +11568,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -11538,27 +11578,27 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -11757,11 +11797,15 @@
           <t>2383.5</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>2274.25</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>1950.6</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>2274.25</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>1950.6</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -12489,62 +12533,62 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
+      <c r="AW13" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS13" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -12743,11 +12787,15 @@
           <t>2347.0</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>2269</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>1931.1</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>2269.0</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>1931.1</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -13475,62 +13523,62 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
+      <c r="AW14" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS14" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AT14" t="inlineStr">
+      <c r="AY14" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -13729,11 +13777,15 @@
           <t>2318.0</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>2261.5</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>1908.1</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>2261.5</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>1908.1</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -14471,52 +14523,52 @@
       </c>
       <c r="AS15" t="inlineStr">
         <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AT15" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -14715,11 +14767,15 @@
           <t>2281.5</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>2253</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>1884.7</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>2253.0</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>1884.7</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -15452,57 +15508,57 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AS16" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
+      <c r="AY16" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -15701,11 +15757,15 @@
           <t>2247.5</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>2237.75</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>1862.4</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>2237.75</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>1862.4</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -16438,57 +16498,57 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AS17" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
+      <c r="AY17" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -16687,11 +16747,15 @@
           <t>2217.0</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>2209</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>1838.3</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>2209.0</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>1838.3</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -17419,62 +17483,62 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV18" t="inlineStr">
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -17673,11 +17737,15 @@
           <t>2182.5</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>2176.25</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>1814.7</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>2176.25</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>1814.7</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -18405,62 +18473,62 @@
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -18659,11 +18727,15 @@
           <t>2167.5</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>2141</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>1794.6</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>2141.0</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>1794.6</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
@@ -19416,7 +19488,7 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
@@ -19431,7 +19503,7 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -19446,7 +19518,7 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -19645,11 +19717,15 @@
           <t>233.15</t>
         </is>
       </c>
-      <c r="CQ20" t="n">
-        <v>231.5</v>
-      </c>
-      <c r="CR20" t="n">
-        <v>237.35</v>
+      <c r="CQ20" t="inlineStr">
+        <is>
+          <t>231.5</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>237.35</t>
+        </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
@@ -20402,7 +20478,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -20417,7 +20493,7 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
@@ -20432,7 +20508,7 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
@@ -20631,11 +20707,15 @@
           <t>231.25</t>
         </is>
       </c>
-      <c r="CQ21" t="n">
-        <v>231.88</v>
-      </c>
-      <c r="CR21" t="n">
-        <v>237.65</v>
+      <c r="CQ21" t="inlineStr">
+        <is>
+          <t>231.88</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>237.65</t>
+        </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
@@ -21383,12 +21463,12 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -21403,7 +21483,7 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
@@ -21418,7 +21498,7 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
@@ -21617,11 +21697,15 @@
           <t>229.9</t>
         </is>
       </c>
-      <c r="CQ22" t="n">
-        <v>232.55</v>
-      </c>
-      <c r="CR22" t="n">
-        <v>237.84</v>
+      <c r="CQ22" t="inlineStr">
+        <is>
+          <t>232.55</t>
+        </is>
+      </c>
+      <c r="CR22" t="inlineStr">
+        <is>
+          <t>237.84</t>
+        </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
@@ -22374,7 +22458,7 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
@@ -22389,7 +22473,7 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
@@ -22404,7 +22488,7 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
@@ -22603,11 +22687,15 @@
           <t>228.5</t>
         </is>
       </c>
-      <c r="CQ23" t="n">
-        <v>232.95</v>
-      </c>
-      <c r="CR23" t="n">
-        <v>237.82</v>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>232.95</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>237.82</t>
+        </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
@@ -23355,12 +23443,12 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
@@ -23375,7 +23463,7 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
@@ -23385,12 +23473,12 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
@@ -23589,11 +23677,15 @@
           <t>227.5</t>
         </is>
       </c>
-      <c r="CQ24" t="n">
-        <v>233.68</v>
-      </c>
-      <c r="CR24" t="n">
-        <v>237.86</v>
+      <c r="CQ24" t="inlineStr">
+        <is>
+          <t>233.68</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>237.86</t>
+        </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
@@ -24346,7 +24438,7 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
@@ -24361,7 +24453,7 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
@@ -24371,12 +24463,12 @@
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
@@ -24575,11 +24667,15 @@
           <t>226.4</t>
         </is>
       </c>
-      <c r="CQ25" t="n">
-        <v>234.02</v>
-      </c>
-      <c r="CR25" t="n">
-        <v>238.24</v>
+      <c r="CQ25" t="inlineStr">
+        <is>
+          <t>234.02</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>238.24</t>
+        </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
@@ -25332,7 +25428,7 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
@@ -25347,7 +25443,7 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
@@ -25357,12 +25453,12 @@
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
@@ -25561,11 +25657,15 @@
           <t>226.75</t>
         </is>
       </c>
-      <c r="CQ26" t="n">
-        <v>234.62</v>
-      </c>
-      <c r="CR26" t="n">
-        <v>238.98</v>
+      <c r="CQ26" t="inlineStr">
+        <is>
+          <t>234.62</t>
+        </is>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>238.98</t>
+        </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
@@ -26318,7 +26418,7 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -26333,7 +26433,7 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -26343,12 +26443,12 @@
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
@@ -26547,11 +26647,15 @@
           <t>227.0</t>
         </is>
       </c>
-      <c r="CQ27" t="n">
-        <v>234.62</v>
-      </c>
-      <c r="CR27" t="n">
-        <v>239.26</v>
+      <c r="CQ27" t="inlineStr">
+        <is>
+          <t>234.62</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
+          <t>239.26</t>
+        </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
@@ -27304,7 +27408,7 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
@@ -27319,7 +27423,7 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
@@ -27329,12 +27433,12 @@
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
@@ -27533,11 +27637,15 @@
           <t>227.55</t>
         </is>
       </c>
-      <c r="CQ28" t="n">
-        <v>234.45</v>
-      </c>
-      <c r="CR28" t="n">
-        <v>239.76</v>
+      <c r="CQ28" t="inlineStr">
+        <is>
+          <t>234.45</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
+          <t>239.76</t>
+        </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
@@ -28270,57 +28378,57 @@
       </c>
       <c r="AR29" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AS29" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AT29" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
@@ -28519,11 +28627,15 @@
           <t>297.05</t>
         </is>
       </c>
-      <c r="CQ29" t="n">
-        <v>280.98</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>260.64</v>
+      <c r="CQ29" t="inlineStr">
+        <is>
+          <t>280.98</t>
+        </is>
+      </c>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>260.64</t>
+        </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
@@ -29251,62 +29363,62 @@
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR30" t="inlineStr">
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS30" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AT30" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
@@ -29505,11 +29617,15 @@
           <t>293.65</t>
         </is>
       </c>
-      <c r="CQ30" t="n">
-        <v>279.73</v>
-      </c>
-      <c r="CR30" t="n">
-        <v>260.63</v>
+      <c r="CQ30" t="inlineStr">
+        <is>
+          <t>279.73</t>
+        </is>
+      </c>
+      <c r="CR30" t="inlineStr">
+        <is>
+          <t>260.63</t>
+        </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
@@ -30237,62 +30353,62 @@
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AT31" t="inlineStr">
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
@@ -30491,11 +30607,15 @@
           <t>289.75</t>
         </is>
       </c>
-      <c r="CQ31" t="n">
-        <v>278.88</v>
-      </c>
-      <c r="CR31" t="n">
-        <v>260.29</v>
+      <c r="CQ31" t="inlineStr">
+        <is>
+          <t>278.88</t>
+        </is>
+      </c>
+      <c r="CR31" t="inlineStr">
+        <is>
+          <t>260.29</t>
+        </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
@@ -31223,62 +31343,62 @@
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR32" t="inlineStr">
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS32" t="inlineStr">
+      <c r="AX32" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT32" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
@@ -31477,11 +31597,15 @@
           <t>286.45</t>
         </is>
       </c>
-      <c r="CQ32" t="n">
-        <v>277</v>
-      </c>
-      <c r="CR32" t="n">
-        <v>259.81</v>
+      <c r="CQ32" t="inlineStr">
+        <is>
+          <t>277.0</t>
+        </is>
+      </c>
+      <c r="CR32" t="inlineStr">
+        <is>
+          <t>259.81</t>
+        </is>
       </c>
       <c r="CS32" t="inlineStr">
         <is>
@@ -32209,62 +32333,62 @@
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR33" t="inlineStr">
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS33" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AT33" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
@@ -32463,11 +32587,15 @@
           <t>283.3</t>
         </is>
       </c>
-      <c r="CQ33" t="n">
-        <v>275.77</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>259.65</v>
+      <c r="CQ33" t="inlineStr">
+        <is>
+          <t>275.77</t>
+        </is>
+      </c>
+      <c r="CR33" t="inlineStr">
+        <is>
+          <t>259.65</t>
+        </is>
       </c>
       <c r="CS33" t="inlineStr">
         <is>
@@ -33195,62 +33323,62 @@
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR34" t="inlineStr">
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
@@ -33449,11 +33577,15 @@
           <t>279.35</t>
         </is>
       </c>
-      <c r="CQ34" t="n">
-        <v>272.6</v>
-      </c>
-      <c r="CR34" t="n">
-        <v>259.79</v>
+      <c r="CQ34" t="inlineStr">
+        <is>
+          <t>272.6</t>
+        </is>
+      </c>
+      <c r="CR34" t="inlineStr">
+        <is>
+          <t>259.79</t>
+        </is>
       </c>
       <c r="CS34" t="inlineStr">
         <is>
@@ -34181,62 +34313,62 @@
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT35" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
@@ -34435,11 +34567,15 @@
           <t>275.95</t>
         </is>
       </c>
-      <c r="CQ35" t="n">
-        <v>269.6</v>
-      </c>
-      <c r="CR35" t="n">
-        <v>259.85</v>
+      <c r="CQ35" t="inlineStr">
+        <is>
+          <t>269.6</t>
+        </is>
+      </c>
+      <c r="CR35" t="inlineStr">
+        <is>
+          <t>259.85</t>
+        </is>
       </c>
       <c r="CS35" t="inlineStr">
         <is>
@@ -35167,62 +35303,62 @@
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AT36" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
@@ -35421,11 +35557,15 @@
           <t>271.1</t>
         </is>
       </c>
-      <c r="CQ36" t="n">
-        <v>265.73</v>
-      </c>
-      <c r="CR36" t="n">
-        <v>259.34</v>
+      <c r="CQ36" t="inlineStr">
+        <is>
+          <t>265.73</t>
+        </is>
+      </c>
+      <c r="CR36" t="inlineStr">
+        <is>
+          <t>259.34</t>
+        </is>
       </c>
       <c r="CS36" t="inlineStr">
         <is>
@@ -36178,37 +36318,37 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
@@ -36407,11 +36547,15 @@
           <t>268.25</t>
         </is>
       </c>
-      <c r="CQ37" t="n">
-        <v>262.6</v>
-      </c>
-      <c r="CR37" t="n">
-        <v>259.45</v>
+      <c r="CQ37" t="inlineStr">
+        <is>
+          <t>262.6</t>
+        </is>
+      </c>
+      <c r="CR37" t="inlineStr">
+        <is>
+          <t>259.45</t>
+        </is>
       </c>
       <c r="CS37" t="inlineStr">
         <is>
@@ -37154,47 +37298,47 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
@@ -37393,11 +37537,15 @@
           <t>2476.5</t>
         </is>
       </c>
-      <c r="CQ38" t="n">
-        <v>2448.25</v>
-      </c>
-      <c r="CR38" t="n">
-        <v>2403.9</v>
+      <c r="CQ38" t="inlineStr">
+        <is>
+          <t>2448.25</t>
+        </is>
+      </c>
+      <c r="CR38" t="inlineStr">
+        <is>
+          <t>2403.9</t>
+        </is>
       </c>
       <c r="CS38" t="inlineStr">
         <is>
@@ -37513,7 +37661,7 @@
       </c>
       <c r="DQ38" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR38" t="inlineStr">
@@ -38135,52 +38283,52 @@
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
@@ -38379,11 +38527,15 @@
           <t>2464.5</t>
         </is>
       </c>
-      <c r="CQ39" t="n">
-        <v>2442.5</v>
-      </c>
-      <c r="CR39" t="n">
-        <v>2401.9</v>
+      <c r="CQ39" t="inlineStr">
+        <is>
+          <t>2442.5</t>
+        </is>
+      </c>
+      <c r="CR39" t="inlineStr">
+        <is>
+          <t>2401.9</t>
+        </is>
       </c>
       <c r="CS39" t="inlineStr">
         <is>
@@ -38499,7 +38651,7 @@
       </c>
       <c r="DQ39" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR39" t="inlineStr">
@@ -39121,52 +39273,52 @@
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
@@ -39365,11 +39517,15 @@
           <t>2452.0</t>
         </is>
       </c>
-      <c r="CQ40" t="n">
-        <v>2439</v>
-      </c>
-      <c r="CR40" t="n">
-        <v>2399.9</v>
+      <c r="CQ40" t="inlineStr">
+        <is>
+          <t>2439.0</t>
+        </is>
+      </c>
+      <c r="CR40" t="inlineStr">
+        <is>
+          <t>2399.9</t>
+        </is>
       </c>
       <c r="CS40" t="inlineStr">
         <is>
@@ -39485,7 +39641,7 @@
       </c>
       <c r="DQ40" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR40" t="inlineStr">
@@ -40102,57 +40258,57 @@
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
@@ -40351,11 +40507,15 @@
           <t>2442.0</t>
         </is>
       </c>
-      <c r="CQ41" t="n">
-        <v>2435.25</v>
-      </c>
-      <c r="CR41" t="n">
-        <v>2396.7</v>
+      <c r="CQ41" t="inlineStr">
+        <is>
+          <t>2435.25</t>
+        </is>
+      </c>
+      <c r="CR41" t="inlineStr">
+        <is>
+          <t>2396.7</t>
+        </is>
       </c>
       <c r="CS41" t="inlineStr">
         <is>
@@ -40471,7 +40631,7 @@
       </c>
       <c r="DQ41" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR41" t="inlineStr">
@@ -41088,57 +41248,57 @@
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
@@ -41337,11 +41497,15 @@
           <t>2435.5</t>
         </is>
       </c>
-      <c r="CQ42" t="n">
-        <v>2432.5</v>
-      </c>
-      <c r="CR42" t="n">
-        <v>2393</v>
+      <c r="CQ42" t="inlineStr">
+        <is>
+          <t>2432.5</t>
+        </is>
+      </c>
+      <c r="CR42" t="inlineStr">
+        <is>
+          <t>2393.0</t>
+        </is>
       </c>
       <c r="CS42" t="inlineStr">
         <is>
@@ -41457,7 +41621,7 @@
       </c>
       <c r="DQ42" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR42" t="inlineStr">
@@ -42069,22 +42233,22 @@
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
@@ -42094,37 +42258,37 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
@@ -42323,11 +42487,15 @@
           <t>2433.0</t>
         </is>
       </c>
-      <c r="CQ43" t="n">
-        <v>2429.25</v>
-      </c>
-      <c r="CR43" t="n">
-        <v>2392.9</v>
+      <c r="CQ43" t="inlineStr">
+        <is>
+          <t>2429.25</t>
+        </is>
+      </c>
+      <c r="CR43" t="inlineStr">
+        <is>
+          <t>2392.9</t>
+        </is>
       </c>
       <c r="CS43" t="inlineStr">
         <is>
@@ -42443,7 +42611,7 @@
       </c>
       <c r="DQ43" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR43" t="inlineStr">
@@ -43060,32 +43228,32 @@
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -43095,22 +43263,22 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
@@ -43309,11 +43477,15 @@
           <t>2429.5</t>
         </is>
       </c>
-      <c r="CQ44" t="n">
-        <v>2425</v>
-      </c>
-      <c r="CR44" t="n">
-        <v>2391.7</v>
+      <c r="CQ44" t="inlineStr">
+        <is>
+          <t>2425.0</t>
+        </is>
+      </c>
+      <c r="CR44" t="inlineStr">
+        <is>
+          <t>2391.7</t>
+        </is>
       </c>
       <c r="CS44" t="inlineStr">
         <is>
@@ -43429,7 +43601,7 @@
       </c>
       <c r="DQ44" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR44" t="inlineStr">
@@ -44046,57 +44218,57 @@
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW45" t="inlineStr">
+      <c r="AX45" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
@@ -44295,11 +44467,15 @@
           <t>2430.5</t>
         </is>
       </c>
-      <c r="CQ45" t="n">
-        <v>2422</v>
-      </c>
-      <c r="CR45" t="n">
-        <v>2390.9</v>
+      <c r="CQ45" t="inlineStr">
+        <is>
+          <t>2422.0</t>
+        </is>
+      </c>
+      <c r="CR45" t="inlineStr">
+        <is>
+          <t>2390.9</t>
+        </is>
       </c>
       <c r="CS45" t="inlineStr">
         <is>
@@ -45027,62 +45203,62 @@
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV46" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
@@ -45281,11 +45457,15 @@
           <t>2428.5</t>
         </is>
       </c>
-      <c r="CQ46" t="n">
-        <v>2416.75</v>
-      </c>
-      <c r="CR46" t="n">
-        <v>2390.1</v>
+      <c r="CQ46" t="inlineStr">
+        <is>
+          <t>2416.75</t>
+        </is>
+      </c>
+      <c r="CR46" t="inlineStr">
+        <is>
+          <t>2390.1</t>
+        </is>
       </c>
       <c r="CS46" t="inlineStr">
         <is>
@@ -46023,52 +46203,52 @@
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
@@ -46267,11 +46447,15 @@
           <t>156.55</t>
         </is>
       </c>
-      <c r="CQ47" t="n">
-        <v>147.4</v>
-      </c>
-      <c r="CR47" t="n">
-        <v>131.88</v>
+      <c r="CQ47" t="inlineStr">
+        <is>
+          <t>147.4</t>
+        </is>
+      </c>
+      <c r="CR47" t="inlineStr">
+        <is>
+          <t>131.88</t>
+        </is>
       </c>
       <c r="CS47" t="inlineStr">
         <is>
@@ -46387,7 +46571,7 @@
       </c>
       <c r="DQ47" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR47" t="inlineStr">
@@ -47009,52 +47193,52 @@
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
@@ -47253,11 +47437,15 @@
           <t>154.6</t>
         </is>
       </c>
-      <c r="CQ48" t="n">
-        <v>145.62</v>
-      </c>
-      <c r="CR48" t="n">
-        <v>131.43</v>
+      <c r="CQ48" t="inlineStr">
+        <is>
+          <t>145.62</t>
+        </is>
+      </c>
+      <c r="CR48" t="inlineStr">
+        <is>
+          <t>131.43</t>
+        </is>
       </c>
       <c r="CS48" t="inlineStr">
         <is>
@@ -47373,7 +47561,7 @@
       </c>
       <c r="DQ48" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR48" t="inlineStr">
@@ -47990,57 +48178,57 @@
       </c>
       <c r="AR49" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AS49" t="inlineStr">
+      <c r="AX49" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AT49" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV49" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
@@ -48239,11 +48427,15 @@
           <t>152.3</t>
         </is>
       </c>
-      <c r="CQ49" t="n">
-        <v>144.18</v>
-      </c>
-      <c r="CR49" t="n">
-        <v>130.89</v>
+      <c r="CQ49" t="inlineStr">
+        <is>
+          <t>144.18</t>
+        </is>
+      </c>
+      <c r="CR49" t="inlineStr">
+        <is>
+          <t>130.89</t>
+        </is>
       </c>
       <c r="CS49" t="inlineStr">
         <is>
@@ -48359,7 +48551,7 @@
       </c>
       <c r="DQ49" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR49" t="inlineStr">
@@ -48976,57 +49168,57 @@
       </c>
       <c r="AR50" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AS50" t="inlineStr">
+      <c r="AX50" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AT50" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV50" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
@@ -49225,11 +49417,15 @@
           <t>151.1</t>
         </is>
       </c>
-      <c r="CQ50" t="n">
-        <v>142.9</v>
-      </c>
-      <c r="CR50" t="n">
-        <v>130.4</v>
+      <c r="CQ50" t="inlineStr">
+        <is>
+          <t>142.9</t>
+        </is>
+      </c>
+      <c r="CR50" t="inlineStr">
+        <is>
+          <t>130.4</t>
+        </is>
       </c>
       <c r="CS50" t="inlineStr">
         <is>
@@ -49345,7 +49541,7 @@
       </c>
       <c r="DQ50" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR50" t="inlineStr">
@@ -49957,62 +50153,62 @@
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR51" t="inlineStr">
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS51" t="inlineStr">
+      <c r="AX51" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT51" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV51" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
@@ -50211,11 +50407,15 @@
           <t>149.8</t>
         </is>
       </c>
-      <c r="CQ51" t="n">
-        <v>141.72</v>
-      </c>
-      <c r="CR51" t="n">
-        <v>130.21</v>
+      <c r="CQ51" t="inlineStr">
+        <is>
+          <t>141.72</t>
+        </is>
+      </c>
+      <c r="CR51" t="inlineStr">
+        <is>
+          <t>130.21</t>
+        </is>
       </c>
       <c r="CS51" t="inlineStr">
         <is>
@@ -50331,7 +50531,7 @@
       </c>
       <c r="DQ51" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR51" t="inlineStr">
@@ -50943,62 +51143,62 @@
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR52" t="inlineStr">
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS52" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AT52" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV52" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
@@ -51197,11 +51397,15 @@
           <t>148.65</t>
         </is>
       </c>
-      <c r="CQ52" t="n">
-        <v>139.95</v>
-      </c>
-      <c r="CR52" t="n">
-        <v>130.33</v>
+      <c r="CQ52" t="inlineStr">
+        <is>
+          <t>139.95</t>
+        </is>
+      </c>
+      <c r="CR52" t="inlineStr">
+        <is>
+          <t>130.33</t>
+        </is>
       </c>
       <c r="CS52" t="inlineStr">
         <is>
@@ -51317,7 +51521,7 @@
       </c>
       <c r="DQ52" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR52" t="inlineStr">
@@ -51929,62 +52133,62 @@
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR53" t="inlineStr">
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS53" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AT53" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV53" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
@@ -52183,11 +52387,15 @@
           <t>146.8</t>
         </is>
       </c>
-      <c r="CQ53" t="n">
-        <v>138.12</v>
-      </c>
-      <c r="CR53" t="n">
-        <v>130.45</v>
+      <c r="CQ53" t="inlineStr">
+        <is>
+          <t>138.12</t>
+        </is>
+      </c>
+      <c r="CR53" t="inlineStr">
+        <is>
+          <t>130.45</t>
+        </is>
       </c>
       <c r="CS53" t="inlineStr">
         <is>
@@ -52303,7 +52511,7 @@
       </c>
       <c r="DQ53" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR53" t="inlineStr">
@@ -52915,62 +53123,62 @@
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS54" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT54" t="inlineStr">
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV54" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
@@ -53169,11 +53377,15 @@
           <t>144.5</t>
         </is>
       </c>
-      <c r="CQ54" t="n">
-        <v>136.38</v>
-      </c>
-      <c r="CR54" t="n">
-        <v>130.27</v>
+      <c r="CQ54" t="inlineStr">
+        <is>
+          <t>136.38</t>
+        </is>
+      </c>
+      <c r="CR54" t="inlineStr">
+        <is>
+          <t>130.27</t>
+        </is>
       </c>
       <c r="CS54" t="inlineStr">
         <is>
@@ -53901,62 +54113,62 @@
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT55" t="inlineStr">
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV55" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
@@ -54155,11 +54367,15 @@
           <t>143.1</t>
         </is>
       </c>
-      <c r="CQ55" t="n">
-        <v>134.7</v>
-      </c>
-      <c r="CR55" t="n">
-        <v>130.2</v>
+      <c r="CQ55" t="inlineStr">
+        <is>
+          <t>134.7</t>
+        </is>
+      </c>
+      <c r="CR55" t="inlineStr">
+        <is>
+          <t>130.2</t>
+        </is>
       </c>
       <c r="CS55" t="inlineStr">
         <is>
@@ -54912,7 +55128,7 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
@@ -54927,22 +55143,22 @@
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
@@ -55141,11 +55357,15 @@
           <t>18.065</t>
         </is>
       </c>
-      <c r="CQ56" t="n">
-        <v>18.41</v>
-      </c>
-      <c r="CR56" t="n">
-        <v>18.69</v>
+      <c r="CQ56" t="inlineStr">
+        <is>
+          <t>18.41</t>
+        </is>
+      </c>
+      <c r="CR56" t="inlineStr">
+        <is>
+          <t>18.69</t>
+        </is>
       </c>
       <c r="CS56" t="inlineStr">
         <is>
@@ -55898,7 +56118,7 @@
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
@@ -55913,22 +56133,22 @@
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
@@ -56127,11 +56347,15 @@
           <t>18.07</t>
         </is>
       </c>
-      <c r="CQ57" t="n">
-        <v>18.46</v>
-      </c>
-      <c r="CR57" t="n">
-        <v>18.71</v>
+      <c r="CQ57" t="inlineStr">
+        <is>
+          <t>18.46</t>
+        </is>
+      </c>
+      <c r="CR57" t="inlineStr">
+        <is>
+          <t>18.71</t>
+        </is>
       </c>
       <c r="CS57" t="inlineStr">
         <is>
@@ -56884,7 +57108,7 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
@@ -56899,22 +57123,22 @@
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
@@ -57113,11 +57337,15 @@
           <t>18.07</t>
         </is>
       </c>
-      <c r="CQ58" t="n">
-        <v>18.52</v>
-      </c>
-      <c r="CR58" t="n">
-        <v>18.73</v>
+      <c r="CQ58" t="inlineStr">
+        <is>
+          <t>18.52</t>
+        </is>
+      </c>
+      <c r="CR58" t="inlineStr">
+        <is>
+          <t>18.73</t>
+        </is>
       </c>
       <c r="CS58" t="inlineStr">
         <is>
@@ -57870,7 +58098,7 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
@@ -57885,22 +58113,22 @@
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
@@ -58099,11 +58327,15 @@
           <t>18.08</t>
         </is>
       </c>
-      <c r="CQ59" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="CR59" t="n">
-        <v>18.74</v>
+      <c r="CQ59" t="inlineStr">
+        <is>
+          <t>18.57</t>
+        </is>
+      </c>
+      <c r="CR59" t="inlineStr">
+        <is>
+          <t>18.74</t>
+        </is>
       </c>
       <c r="CS59" t="inlineStr">
         <is>
@@ -58856,7 +59088,7 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
@@ -58871,22 +59103,22 @@
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
@@ -59085,11 +59317,15 @@
           <t>18.09</t>
         </is>
       </c>
-      <c r="CQ60" t="n">
-        <v>18.63</v>
-      </c>
-      <c r="CR60" t="n">
-        <v>18.76</v>
+      <c r="CQ60" t="inlineStr">
+        <is>
+          <t>18.63</t>
+        </is>
+      </c>
+      <c r="CR60" t="inlineStr">
+        <is>
+          <t>18.76</t>
+        </is>
       </c>
       <c r="CS60" t="inlineStr">
         <is>
@@ -59842,7 +60078,7 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
@@ -59857,22 +60093,22 @@
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
@@ -60071,11 +60307,15 @@
           <t>18.11</t>
         </is>
       </c>
-      <c r="CQ61" t="n">
-        <v>18.69</v>
-      </c>
-      <c r="CR61" t="n">
-        <v>18.78</v>
+      <c r="CQ61" t="inlineStr">
+        <is>
+          <t>18.69</t>
+        </is>
+      </c>
+      <c r="CR61" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
       </c>
       <c r="CS61" t="inlineStr">
         <is>
@@ -60818,47 +61058,47 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV62" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV62" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
@@ -61057,11 +61297,15 @@
           <t>18.26</t>
         </is>
       </c>
-      <c r="CQ62" t="n">
-        <v>18.76</v>
-      </c>
-      <c r="CR62" t="n">
-        <v>18.81</v>
+      <c r="CQ62" t="inlineStr">
+        <is>
+          <t>18.76</t>
+        </is>
+      </c>
+      <c r="CR62" t="inlineStr">
+        <is>
+          <t>18.81</t>
+        </is>
       </c>
       <c r="CS62" t="inlineStr">
         <is>
@@ -61804,7 +62048,7 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
@@ -61814,7 +62058,7 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
@@ -61829,22 +62073,22 @@
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
@@ -62043,11 +62287,15 @@
           <t>18.385</t>
         </is>
       </c>
-      <c r="CQ63" t="n">
-        <v>18.82</v>
-      </c>
-      <c r="CR63" t="n">
-        <v>18.83</v>
+      <c r="CQ63" t="inlineStr">
+        <is>
+          <t>18.82</t>
+        </is>
+      </c>
+      <c r="CR63" t="inlineStr">
+        <is>
+          <t>18.83</t>
+        </is>
       </c>
       <c r="CS63" t="inlineStr">
         <is>
@@ -62790,7 +63038,7 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
@@ -62800,7 +63048,7 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
@@ -62815,22 +63063,22 @@
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
@@ -63029,11 +63277,15 @@
           <t>18.525</t>
         </is>
       </c>
-      <c r="CQ64" t="n">
-        <v>18.88</v>
-      </c>
-      <c r="CR64" t="n">
-        <v>18.85</v>
+      <c r="CQ64" t="inlineStr">
+        <is>
+          <t>18.88</t>
+        </is>
+      </c>
+      <c r="CR64" t="inlineStr">
+        <is>
+          <t>18.85</t>
+        </is>
       </c>
       <c r="CS64" t="inlineStr">
         <is>
@@ -63786,7 +64038,7 @@
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
@@ -63801,22 +64053,22 @@
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
@@ -64015,11 +64267,15 @@
           <t>23.1</t>
         </is>
       </c>
-      <c r="CQ65" t="n">
-        <v>23.13</v>
-      </c>
-      <c r="CR65" t="n">
-        <v>23.35</v>
+      <c r="CQ65" t="inlineStr">
+        <is>
+          <t>23.13</t>
+        </is>
+      </c>
+      <c r="CR65" t="inlineStr">
+        <is>
+          <t>23.35</t>
+        </is>
       </c>
       <c r="CS65" t="inlineStr">
         <is>
@@ -64772,7 +65028,7 @@
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
@@ -64782,27 +65038,27 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
@@ -65001,11 +65257,15 @@
           <t>23.07</t>
         </is>
       </c>
-      <c r="CQ66" t="n">
-        <v>23.12</v>
-      </c>
-      <c r="CR66" t="n">
-        <v>23.34</v>
+      <c r="CQ66" t="inlineStr">
+        <is>
+          <t>23.12</t>
+        </is>
+      </c>
+      <c r="CR66" t="inlineStr">
+        <is>
+          <t>23.34</t>
+        </is>
       </c>
       <c r="CS66" t="inlineStr">
         <is>
@@ -65758,7 +66018,7 @@
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
@@ -65768,27 +66028,27 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
@@ -65987,11 +66247,15 @@
           <t>23.105</t>
         </is>
       </c>
-      <c r="CQ67" t="n">
-        <v>23.11</v>
-      </c>
-      <c r="CR67" t="n">
-        <v>23.34</v>
+      <c r="CQ67" t="inlineStr">
+        <is>
+          <t>23.11</t>
+        </is>
+      </c>
+      <c r="CR67" t="inlineStr">
+        <is>
+          <t>23.34</t>
+        </is>
       </c>
       <c r="CS67" t="inlineStr">
         <is>
@@ -66744,37 +67008,37 @@
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
@@ -66973,11 +67237,15 @@
           <t>23.165</t>
         </is>
       </c>
-      <c r="CQ68" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="CR68" t="n">
-        <v>23.33</v>
+      <c r="CQ68" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="CR68" t="inlineStr">
+        <is>
+          <t>23.33</t>
+        </is>
       </c>
       <c r="CS68" t="inlineStr">
         <is>
@@ -67730,37 +67998,37 @@
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
@@ -67959,11 +68227,15 @@
           <t>23.215</t>
         </is>
       </c>
-      <c r="CQ69" t="n">
-        <v>23.11</v>
-      </c>
-      <c r="CR69" t="n">
-        <v>23.33</v>
+      <c r="CQ69" t="inlineStr">
+        <is>
+          <t>23.11</t>
+        </is>
+      </c>
+      <c r="CR69" t="inlineStr">
+        <is>
+          <t>23.33</t>
+        </is>
       </c>
       <c r="CS69" t="inlineStr">
         <is>
@@ -68716,37 +68988,37 @@
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
@@ -68945,11 +69217,15 @@
           <t>23.235</t>
         </is>
       </c>
-      <c r="CQ70" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="CR70" t="n">
-        <v>23.34</v>
+      <c r="CQ70" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="CR70" t="inlineStr">
+        <is>
+          <t>23.34</t>
+        </is>
       </c>
       <c r="CS70" t="inlineStr">
         <is>
@@ -69702,7 +69978,7 @@
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
@@ -69717,22 +69993,22 @@
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
@@ -69931,11 +70207,15 @@
           <t>23.225</t>
         </is>
       </c>
-      <c r="CQ71" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="CR71" t="n">
-        <v>23.34</v>
+      <c r="CQ71" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="CR71" t="inlineStr">
+        <is>
+          <t>23.34</t>
+        </is>
       </c>
       <c r="CS71" t="inlineStr">
         <is>
@@ -70688,7 +70968,7 @@
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
@@ -70698,27 +70978,27 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
@@ -70917,11 +71197,15 @@
           <t>23.21</t>
         </is>
       </c>
-      <c r="CQ72" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="CR72" t="n">
-        <v>23.34</v>
+      <c r="CQ72" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="CR72" t="inlineStr">
+        <is>
+          <t>23.34</t>
+        </is>
       </c>
       <c r="CS72" t="inlineStr">
         <is>
@@ -71674,7 +71958,7 @@
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
@@ -71684,27 +71968,27 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
@@ -71903,11 +72187,15 @@
           <t>23.19</t>
         </is>
       </c>
-      <c r="CQ73" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="CR73" t="n">
-        <v>23.34</v>
+      <c r="CQ73" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="CR73" t="inlineStr">
+        <is>
+          <t>23.34</t>
+        </is>
       </c>
       <c r="CS73" t="inlineStr">
         <is>
@@ -72660,7 +72948,7 @@
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
@@ -72675,22 +72963,22 @@
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
@@ -72889,11 +73177,15 @@
           <t>702.0</t>
         </is>
       </c>
-      <c r="CQ74" t="n">
-        <v>710.85</v>
-      </c>
-      <c r="CR74" t="n">
-        <v>709.4400000000001</v>
+      <c r="CQ74" t="inlineStr">
+        <is>
+          <t>710.85</t>
+        </is>
+      </c>
+      <c r="CR74" t="inlineStr">
+        <is>
+          <t>709.44</t>
+        </is>
       </c>
       <c r="CS74" t="inlineStr">
         <is>
@@ -73646,7 +73938,7 @@
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
@@ -73661,22 +73953,22 @@
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
@@ -73875,11 +74167,15 @@
           <t>703.4</t>
         </is>
       </c>
-      <c r="CQ75" t="n">
-        <v>713.3</v>
-      </c>
-      <c r="CR75" t="n">
-        <v>709.7</v>
+      <c r="CQ75" t="inlineStr">
+        <is>
+          <t>713.3</t>
+        </is>
+      </c>
+      <c r="CR75" t="inlineStr">
+        <is>
+          <t>709.7</t>
+        </is>
       </c>
       <c r="CS75" t="inlineStr">
         <is>
@@ -74632,7 +74928,7 @@
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
@@ -74647,22 +74943,22 @@
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
@@ -74861,11 +75157,15 @@
           <t>704.0</t>
         </is>
       </c>
-      <c r="CQ76" t="n">
-        <v>716.95</v>
-      </c>
-      <c r="CR76" t="n">
-        <v>709.78</v>
+      <c r="CQ76" t="inlineStr">
+        <is>
+          <t>716.95</t>
+        </is>
+      </c>
+      <c r="CR76" t="inlineStr">
+        <is>
+          <t>709.78</t>
+        </is>
       </c>
       <c r="CS76" t="inlineStr">
         <is>
@@ -75618,7 +75918,7 @@
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
@@ -75633,22 +75933,22 @@
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
@@ -75847,11 +76147,15 @@
           <t>704.4</t>
         </is>
       </c>
-      <c r="CQ77" t="n">
-        <v>718.75</v>
-      </c>
-      <c r="CR77" t="n">
-        <v>709.28</v>
+      <c r="CQ77" t="inlineStr">
+        <is>
+          <t>718.75</t>
+        </is>
+      </c>
+      <c r="CR77" t="inlineStr">
+        <is>
+          <t>709.28</t>
+        </is>
       </c>
       <c r="CS77" t="inlineStr">
         <is>
@@ -76604,7 +76908,7 @@
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
@@ -76619,22 +76923,22 @@
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
@@ -76833,11 +77137,15 @@
           <t>706.8</t>
         </is>
       </c>
-      <c r="CQ78" t="n">
-        <v>722.1</v>
-      </c>
-      <c r="CR78" t="n">
-        <v>708.62</v>
+      <c r="CQ78" t="inlineStr">
+        <is>
+          <t>722.1</t>
+        </is>
+      </c>
+      <c r="CR78" t="inlineStr">
+        <is>
+          <t>708.62</t>
+        </is>
       </c>
       <c r="CS78" t="inlineStr">
         <is>
@@ -77590,7 +77898,7 @@
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
@@ -77605,22 +77913,22 @@
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
@@ -77819,11 +78127,15 @@
           <t>708.7</t>
         </is>
       </c>
-      <c r="CQ79" t="n">
-        <v>725.65</v>
-      </c>
-      <c r="CR79" t="n">
-        <v>708.46</v>
+      <c r="CQ79" t="inlineStr">
+        <is>
+          <t>725.65</t>
+        </is>
+      </c>
+      <c r="CR79" t="inlineStr">
+        <is>
+          <t>708.46</t>
+        </is>
       </c>
       <c r="CS79" t="inlineStr">
         <is>
@@ -78576,7 +78888,7 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
@@ -78591,22 +78903,22 @@
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
@@ -78805,11 +79117,15 @@
           <t>711.8</t>
         </is>
       </c>
-      <c r="CQ80" t="n">
-        <v>726.3</v>
-      </c>
-      <c r="CR80" t="n">
-        <v>708.5599999999999</v>
+      <c r="CQ80" t="inlineStr">
+        <is>
+          <t>726.3</t>
+        </is>
+      </c>
+      <c r="CR80" t="inlineStr">
+        <is>
+          <t>708.56</t>
+        </is>
       </c>
       <c r="CS80" t="inlineStr">
         <is>
@@ -79562,7 +79878,7 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
@@ -79577,22 +79893,22 @@
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
@@ -79791,11 +80107,15 @@
           <t>713.4</t>
         </is>
       </c>
-      <c r="CQ81" t="n">
-        <v>726.55</v>
-      </c>
-      <c r="CR81" t="n">
-        <v>708.16</v>
+      <c r="CQ81" t="inlineStr">
+        <is>
+          <t>726.55</t>
+        </is>
+      </c>
+      <c r="CR81" t="inlineStr">
+        <is>
+          <t>708.16</t>
+        </is>
       </c>
       <c r="CS81" t="inlineStr">
         <is>
@@ -80538,47 +80858,47 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV82" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
@@ -80777,11 +81097,15 @@
           <t>715.5</t>
         </is>
       </c>
-      <c r="CQ82" t="n">
-        <v>726.25</v>
-      </c>
-      <c r="CR82" t="n">
-        <v>708.34</v>
+      <c r="CQ82" t="inlineStr">
+        <is>
+          <t>726.25</t>
+        </is>
+      </c>
+      <c r="CR82" t="inlineStr">
+        <is>
+          <t>708.34</t>
+        </is>
       </c>
       <c r="CS82" t="inlineStr">
         <is>
@@ -81514,34 +81838,34 @@
       </c>
       <c r="AR83" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AS83" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT83" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV83" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AW83" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="AX83" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -81549,22 +81873,22 @@
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
@@ -81763,11 +82087,15 @@
           <t>25.09</t>
         </is>
       </c>
-      <c r="CQ83" t="n">
-        <v>24.72</v>
-      </c>
-      <c r="CR83" t="n">
-        <v>24.49</v>
+      <c r="CQ83" t="inlineStr">
+        <is>
+          <t>24.72</t>
+        </is>
+      </c>
+      <c r="CR83" t="inlineStr">
+        <is>
+          <t>24.49</t>
+        </is>
       </c>
       <c r="CS83" t="inlineStr">
         <is>
@@ -81883,7 +82211,7 @@
       </c>
       <c r="DQ83" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR83" t="inlineStr">
@@ -82495,62 +82823,62 @@
       </c>
       <c r="AQ84" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT84" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
@@ -82749,11 +83077,15 @@
           <t>24.96</t>
         </is>
       </c>
-      <c r="CQ84" t="n">
-        <v>24.69</v>
-      </c>
-      <c r="CR84" t="n">
-        <v>24.46</v>
+      <c r="CQ84" t="inlineStr">
+        <is>
+          <t>24.69</t>
+        </is>
+      </c>
+      <c r="CR84" t="inlineStr">
+        <is>
+          <t>24.46</t>
+        </is>
       </c>
       <c r="CS84" t="inlineStr">
         <is>
@@ -82869,7 +83201,7 @@
       </c>
       <c r="DQ84" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR84" t="inlineStr">
@@ -83486,17 +83818,17 @@
       </c>
       <c r="AR85" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU85" t="inlineStr">
@@ -83506,37 +83838,37 @@
       </c>
       <c r="AV85" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AW85" t="inlineStr">
+      <c r="AX85" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
+      <c r="AY85" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AY85" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
@@ -83735,11 +84067,15 @@
           <t>24.785</t>
         </is>
       </c>
-      <c r="CQ85" t="n">
-        <v>24.68</v>
-      </c>
-      <c r="CR85" t="n">
-        <v>24.43</v>
+      <c r="CQ85" t="inlineStr">
+        <is>
+          <t>24.68</t>
+        </is>
+      </c>
+      <c r="CR85" t="inlineStr">
+        <is>
+          <t>24.43</t>
+        </is>
       </c>
       <c r="CS85" t="inlineStr">
         <is>
@@ -83855,7 +84191,7 @@
       </c>
       <c r="DQ85" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR85" t="inlineStr">
@@ -84467,22 +84803,22 @@
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
@@ -84492,37 +84828,37 @@
       </c>
       <c r="AV86" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AW86" t="inlineStr">
+      <c r="AX86" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
+      <c r="AY86" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AY86" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
@@ -84721,11 +85057,15 @@
           <t>24.545</t>
         </is>
       </c>
-      <c r="CQ86" t="n">
-        <v>24.58</v>
-      </c>
-      <c r="CR86" t="n">
-        <v>24.38</v>
+      <c r="CQ86" t="inlineStr">
+        <is>
+          <t>24.58</t>
+        </is>
+      </c>
+      <c r="CR86" t="inlineStr">
+        <is>
+          <t>24.38</t>
+        </is>
       </c>
       <c r="CS86" t="inlineStr">
         <is>
@@ -84841,7 +85181,7 @@
       </c>
       <c r="DQ86" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR86" t="inlineStr">
@@ -85453,22 +85793,22 @@
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
@@ -85478,37 +85818,37 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AW87" t="inlineStr">
+      <c r="AX87" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
+      <c r="AY87" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
@@ -85707,11 +86047,15 @@
           <t>24.465</t>
         </is>
       </c>
-      <c r="CQ87" t="n">
-        <v>24.53</v>
-      </c>
-      <c r="CR87" t="n">
-        <v>24.35</v>
+      <c r="CQ87" t="inlineStr">
+        <is>
+          <t>24.53</t>
+        </is>
+      </c>
+      <c r="CR87" t="inlineStr">
+        <is>
+          <t>24.35</t>
+        </is>
       </c>
       <c r="CS87" t="inlineStr">
         <is>
@@ -85827,7 +86171,7 @@
       </c>
       <c r="DQ87" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR87" t="inlineStr">
@@ -86439,22 +86783,22 @@
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
@@ -86464,37 +86808,37 @@
       </c>
       <c r="AV88" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW88" t="inlineStr">
+      <c r="AX88" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
+      <c r="AY88" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AY88" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
@@ -86693,11 +87037,15 @@
           <t>24.42</t>
         </is>
       </c>
-      <c r="CQ88" t="n">
-        <v>24.48</v>
-      </c>
-      <c r="CR88" t="n">
-        <v>24.32</v>
+      <c r="CQ88" t="inlineStr">
+        <is>
+          <t>24.48</t>
+        </is>
+      </c>
+      <c r="CR88" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
       </c>
       <c r="CS88" t="inlineStr">
         <is>
@@ -86813,7 +87161,7 @@
       </c>
       <c r="DQ88" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR88" t="inlineStr">
@@ -87440,17 +87788,17 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
@@ -87460,27 +87808,27 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY89" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
@@ -87679,11 +88027,15 @@
           <t>24.33</t>
         </is>
       </c>
-      <c r="CQ89" t="n">
-        <v>24.41</v>
-      </c>
-      <c r="CR89" t="n">
-        <v>24.28</v>
+      <c r="CQ89" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="CR89" t="inlineStr">
+        <is>
+          <t>24.28</t>
+        </is>
       </c>
       <c r="CS89" t="inlineStr">
         <is>
@@ -88426,7 +88778,7 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
@@ -88436,7 +88788,7 @@
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
@@ -88446,27 +88798,27 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
@@ -88665,11 +89017,15 @@
           <t>24.305</t>
         </is>
       </c>
-      <c r="CQ90" t="n">
-        <v>24.41</v>
-      </c>
-      <c r="CR90" t="n">
-        <v>24.24</v>
+      <c r="CQ90" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="CR90" t="inlineStr">
+        <is>
+          <t>24.24</t>
+        </is>
       </c>
       <c r="CS90" t="inlineStr">
         <is>
@@ -89412,7 +89768,7 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
@@ -89422,7 +89778,7 @@
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
@@ -89432,27 +89788,27 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
@@ -89651,11 +90007,15 @@
           <t>24.32</t>
         </is>
       </c>
-      <c r="CQ91" t="n">
-        <v>24.44</v>
-      </c>
-      <c r="CR91" t="n">
-        <v>24.22</v>
+      <c r="CQ91" t="inlineStr">
+        <is>
+          <t>24.44</t>
+        </is>
+      </c>
+      <c r="CR91" t="inlineStr">
+        <is>
+          <t>24.22</t>
+        </is>
       </c>
       <c r="CS91" t="inlineStr">
         <is>
